--- a/ig/DM-MARS-2026/CodeSystem-tre-r387-type-groupement.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-tre-r387-type-groupement.xlsx
@@ -244,7 +244,7 @@
     <t>Groupement de coopération organique</t>
   </si>
   <si>
-    <t xml:space="preserve"> La coopération organique entre personnes morales se traduit par la création d’une nouvelle structure juridique dotée d’une personnalité morale. Elle s’adosse à différents supports juridiques dont par exemple le GCS (Groupement de Coopération Sanitaire) ou le Groupement de Coopération sociale et médico-sociale (GCSMS). Un GCO est donc représenté par une Personne Morale particulière dite 'tête de groupe'.</t>
+    <t>La coopération organique entre personnes morales se traduit par la création d’une nouvelle structure juridique dotée d’une personnalité morale. Elle s’adosse à différents supports juridiques dont par exemple le GCS (Groupement de Coopération Sanitaire) ou le Groupement de Coopération sociale et médico-sociale (GCSMS). Un GCO est donc représenté par une Personne Morale particulière dite 'tête de groupe'.</t>
   </si>
 </sst>
 </file>
